--- a/src/rodos_corpus/data/corpus/rendered/finance/FIN-LIST-SOGL-TSU-2026.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/finance/FIN-LIST-SOGL-TSU-2026.xlsx
@@ -439,7 +439,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Лист согласования проекта договора поставки с ООО «ТехСнаб-Урал»</t>
+          <t>Лист согласования проекта договора поставки металлопродукции № ТСУ-2026/118</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -506,32 +506,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>п. 3.2 — проект возвращён инициатору: пункт 7.2 проекта исключает неустойку за просрочку поставки, что является отклонением от типовой формы (п. 4.2)</t>
+          <t>п. 3.2 — проект возвращён инициатору: пункт 2.6 разрешает Поставщику односторонне менять цену по подписанным спецификациям и противоречит пункту 12.1 того же проекта; в разделе 6 нет ответственности Поставщика за просрочку поставки</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3.1.1 Повторное рассмотрение после правки</t>
+          <t>3.1.2 Условия оплаты и налоговые последствия</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Юрисконсульт</t>
+          <t>Главный бухгалтер</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>неустойка восстановлена в редакции типовой формы</t>
+          <t>отсрочка 90 календарных дней против 20 дней по ПП-2025/14 — отклонение от типовых условий (п. 4.2), препятствий по налоговым последствиям нет</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3.1.2 Условия оплаты и налоговые последствия</t>
+          <t>3.1.3 Соответствие бюджету ЦФО</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Главный бухгалтер</t>
+          <t>Финансовый директор</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -566,34 +566,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>согласовано</t>
+          <t>согласовано с условием</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>отсрочка 90 календарных дней без обеспечения — нетиповое условие (п. 4.2), передано финансовому директору</t>
+          <t>п. 4.2 — отклонения по пунктам 1.5, 2.3, 4.3 и разделу 6 согласованы в нашей редакции; пункт 2.6 не согласован ни в какой редакции, потому что делает сумму договора неопределимой на дату согласования</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3.1.3 Соответствие бюджету ЦФО</t>
+          <t>3.1.4 Предмет и технические условия</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Финансовый директор</t>
+          <t>Начальник отдела снабжения</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -611,59 +611,61 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>п. 4.2 — нетиповое условие согласовано при снижении отсрочки до 45 календарных дней; скидка сверх матрицы проектом не предусмотрена (п. 4.3)</t>
+          <t>номенклатура и марки стали соответствуют потребности; приёмка по качеству — только после входного контроля ОТК по регламенту ОТК-РЕГЛ-003, срок по пункту 4.3 проекта для этого недостаточен</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3.1.4 Предмет и технические условия</t>
+          <t>Проверка должной осмотрительности до заключения</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Начальник отдела снабжения</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
+          <t>Финансовая служба</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>пройдена</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>24.09.2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>согласовано</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>типовые условия по п. 4.1, замечаний нет</t>
+          <t>п. 4.2 регламента FIN-REGL-ZAKUPKI: закупка у непроверенного поставщика не допускается; заключение FIN-ZAKL-DOLZHOSM-TSU-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5.1 Подписание (сумма до 5 000 000 ₽)</t>
+          <t>5.2 Подписание (сумма свыше 5 000 000 ₽)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Коммерческий директор</t>
+          <t>Генеральный директор</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -673,22 +675,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>подписано</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>плановая сумма 3 800 000 ₽</t>
+          <t>сумма договора 6 200 000 ₽ по пункту 2.2 проекта; ожидается ответ контрагента по разногласию № 1 протокола FIN-PROTOKOL-RAZN-TSU-2026</t>
         </is>
       </c>
     </row>
